--- a/base/ValueSet-DocumentationSection.xlsx
+++ b/base/ValueSet-DocumentationSection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CodeSystem for Smart Guidelines Documentation Section to autogenerate documentation from artifacts</t>
+    <t>Value Set for Smart Guidelines Documentation Section to autogenerate documentation from artifacts</t>
   </si>
   <si>
     <t>Purpose</t>
